--- a/data/Belgium_Cyfun_2025.xlsx
+++ b/data/Belgium_Cyfun_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://digiplace-my.sharepoint.com/personal/aurelien_brun_wavestone_com/Documents/Desktop/mapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3F8920-4C90-426C-A46A-8AF0D76F4FBD}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A55D120C-10D5-4BDE-A9AD-CC99F29182FA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Belgique Cyfun 2025" sheetId="2" r:id="rId1"/>
@@ -9668,43 +9668,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <WS_KM xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">false</WS_KM>
-    <Language xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <i51f003d86e044fa8787db0c1fd77971 xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </i51f003d86e044fa8787db0c1fd77971>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"excel-template-wavestone","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
-</file>
-
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Groups X - Document" ma:contentTypeID="0x0101002FECBCFE27A94FA4A49D56DA0627A7A700D5CF0826E9A3234B8339779C1FAEB6D1" ma:contentTypeVersion="26" ma:contentTypeDescription="Content type used in default document library in Groups for external groups (no extra fields for metadata provided)" ma:contentTypeScope="" ma:versionID="279e6f4b32e9b65a6d75abd62779577b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="0e0560a2-5f28-40fd-a47f-413e3deae4f7" xmlns:ns3="49800bc8-27f6-4a38-98b2-e471baa92d6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="16811575601f31dfff62ec4a7f080727" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10016,15 +9979,76 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"excel-template-wavestone","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <WS_KM xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">false</WS_KM>
+    <Language xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <i51f003d86e044fa8787db0c1fd77971 xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </i51f003d86e044fa8787db0c1fd77971>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AEAD36-3C40-43A4-8069-DD963241733E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F97C02F-FADE-4CE7-BA0C-A8E70A521F21}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="0e0560a2-5f28-40fd-a47f-413e3deae4f7"/>
+    <ds:schemaRef ds:uri="49800bc8-27f6-4a38-98b2-e471baa92d6a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6833886D-AFD0-4394-A643-4CABE4FE0F96}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BA3DF0-87BD-4820-849B-A09A7499F975}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD40D982-8286-4B8F-A856-9520176C5B63}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -10042,34 +10066,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BA3DF0-87BD-4820-849B-A09A7499F975}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6833886D-AFD0-4394-A643-4CABE4FE0F96}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F97C02F-FADE-4CE7-BA0C-A8E70A521F21}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AEAD36-3C40-43A4-8069-DD963241733E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="0e0560a2-5f28-40fd-a47f-413e3deae4f7"/>
-    <ds:schemaRef ds:uri="49800bc8-27f6-4a38-98b2-e471baa92d6a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>